--- a/Results/Exam_Output_6.xlsx
+++ b/Results/Exam_Output_6.xlsx
@@ -453,97 +453,25 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>CS 203_1/10 : UG1 (PC) Strength : 10.0
-CS 203_9/10 : UG1 (PC) Strength : 10.0
-ME 204_1/5 : UG1 (PC) Strength : 9.0
-ME 204_5/5 : UG1 (PC) Strength : 5.0
-CL 204_1/2 : UG2 (PC) Strength : 6.0
-CS 203_3/10 : UG2 (PC) Strength : 10.0
-CS 203_7/10 : UG2 (PC) Strength : 10.0
-CS 203_8/10 : UG2 (PC) Strength : 10.0
-PH 101_22/26 : UG2 (PC) Strength : 10.0
-PH 101_24/26 : UG2 (PC) Strength : 10.0
-PH 101_25/26 : UG2 (PC) Strength : 10.0
-PH 101_26/26 : UG2 (PC) Strength : 3.0
-CE 201_2/2 : UG3 (PC) Strength : 6.0
-CL 204_2/2 : UG3 (PC) Strength : 6.0
-CS 203_2/10 : UG3 (PC) Strength : 10.0
-CS 203_5/10 : UG3 (PC) Strength : 10.0
-CS 203_6/10 : UG3 (PC) Strength : 10.0
-ME 204_3/5 : UG3 (PC) Strength : 9.0
-PH 101_3/26 : UG3 (PC) Strength : 10.0
-PH 101_5/26 : UG3 (PC) Strength : 10.0
-CS 203_10/10 : UG4 (PC) Strength : 5.0
-ME 204_2/5 : UG4 (PC) Strength : 9.0
-ME 204_4/5 : UG4 (PC) Strength : 9.0
-PH 101_1/26 : UG4 (PC) Strength : 10.0
-PH 101_11/26 : UG4 (PC) Strength : 10.0
-PH 101_19/26 : UG4 (PC) Strength : 10.0
-PH 101_21/26 : UG4 (PC) Strength : 10.0
-PH 101_9/26 : UG4 (PC) Strength : 10.0
-PH 103_1/3 : UG4 (PC) Strength : 10.0
-PH 103_3/3 : UG4 (PC) Strength : 10.0
-PH 101_7/26 : UG5 (PC) Strength : 10.0
-CE 201_1/2 : F300 (PC) Strength : 6.0
-CS 203_4/10 : F300 (PC) Strength : 10.0
-PH 101_10/26 : F300 (PC) Strength : 10.0
-PH 101_12/26 : F300 (PC) Strength : 10.0
-PH 101_13/26 : F300 (PC) Strength : 10.0
-PH 101_14/26 : F300 (PC) Strength : 10.0
-PH 101_15/26 : F300 (PC) Strength : 10.0
-PH 101_16/26 : F300 (PC) Strength : 10.0
-PH 101_17/26 : F300 (PC) Strength : 10.0
-PH 101_18/26 : F300 (PC) Strength : 10.0
-PH 101_2/26 : F300 (PC) Strength : 10.0
-PH 101_20/26 : F300 (PC) Strength : 10.0
-PH 101_23/26 : F300 (PC) Strength : 10.0
-PH 101_4/26 : F300 (PC) Strength : 10.0
-PH 101_6/26 : F300 (PC) Strength : 10.0
-PH 101_8/26 : F300 (PC) Strength : 10.0
-PH 103_2/3 : F300 (PC) Strength : 10.0
-PH 201_1/2 : F300 (PC) Strength : 6.0
-PH 201_2/2 : F300 (PC) Strength : 5.0
-CE 601_1/1 : 21 (WALMI) Strength : 6.0
-ME 305_1/4 : 115 (WALMI) Strength : 10.0
-ME 305_4/4 : 23 (WALMI) Strength : 10.0
-PH 304_1/1 : 214 (WALMI) Strength : 7.0
-ME 305_2/4 : 215 (WALMI) Strength : 10.0
-ME 305_3/4 : Auditorium (WALMI) Strength : 10.0</t>
+          <t>CE 601
+CS 205
+EE 202
+EE 229
+EE 634
+HS 425
+HS 433
+MA 101
+ME 220
+ME 607
+ME 630</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>CH 202_3/3 : UG2 (PC) Strength : 10.0
-CS 205_10/10 : UG2 (PC) Strength : 3.0
-ME 203_6/8 : UG2 (PC) Strength : 9.0
-ME 203_8/8 : UG2 (PC) Strength : 8.0
-CH 202_1/3 : UG3 (PC) Strength : 10.0
-CS 205_7/10 : UG3 (PC) Strength : 10.0
-ME 203_1/8 : UG3 (PC) Strength : 9.0
-ME 203_2/8 : UG3 (PC) Strength : 9.0
-ME 203_4/8 : UG3 (PC) Strength : 9.0
-ME 203_5/8 : UG3 (PC) Strength : 9.0
-CS 205_1/10 : UG4 (PC) Strength : 10.0
-CS 205_3/10 : UG4 (PC) Strength : 10.0
-CS 205_5/10 : UG4 (PC) Strength : 10.0
-CS 205_6/10 : UG4 (PC) Strength : 10.0
-ME 203_3/8 : UG4 (PC) Strength : 9.0
-ME 203_7/8 : UG6 (PC) Strength : 9.0
-CH 202_2/3 : F300 (PC) Strength : 10.0
-CS 205_2/10 : F300 (PC) Strength : 10.0
-CS 205_4/10 : F300 (PC) Strength : 10.0
-CS 205_8/10 : F300 (PC) Strength : 10.0
-CS 205_9/10 : F300 (PC) Strength : 10.0
-EE 689_1/5 : 115 (WALMI) Strength : 9.0
-EE 689_4/5 : 115 (WALMI) Strength : 9.0
-EE 689_2/5 : 119 (WALMI) Strength : 9.0
-ME 643_1/2 : 22 (WALMI) Strength : 10.0
-EE 689_3/5 : 117 (WALMI) Strength : 9.0
-ME 421_1/1 : 23 (WALMI) Strength : 10.0
-CS 810_1/2 : Central Hall (WALMI) Strength : 6.0
-EE 689_5/5 : 215 (WALMI) Strength : 5.0
-ME 643_2/2 : 203 (WALMI) Strength : 9.0
-CS 810_2/2 : Auditorium (WALMI) Strength : 5.0</t>
+          <t>CH 202
+CH 204
+HS 409
+ME 203</t>
         </is>
       </c>
     </row>
@@ -555,89 +483,25 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>CH 102_10/26 : UG1 (PC) Strength : 10.0
-CH 102_11/26 : UG1 (PC) Strength : 10.0
-CH 102_19/26 : UG2 (PC) Strength : 10.0
-CH 102_2/26 : UG2 (PC) Strength : 10.0
-CH 102_8/26 : UG2 (PC) Strength : 10.0
-ME 201_3/7 : UG2 (PC) Strength : 10.0
-CH 102_20/26 : UG3 (PC) Strength : 10.0
-CH 102_22/26 : UG3 (PC) Strength : 10.0
-CH 102_3/26 : UG3 (PC) Strength : 10.0
-EE 205_1/5 : UG3 (PC) Strength : 10.0
-EE 205_3/5 : UG3 (PC) Strength : 10.0
-EE 205_4/5 : UG3 (PC) Strength : 10.0
-CH 102_14/26 : UG4 (PC) Strength : 10.0
-CH 102_23/26 : UG4 (PC) Strength : 10.0
-CH 102_24/26 : UG4 (PC) Strength : 10.0
-CH 102_25/26 : UG4 (PC) Strength : 10.0
-CH 102_9/26 : UG4 (PC) Strength : 10.0
-ME 201_1/7 : UG4 (PC) Strength : 10.0
-ME 201_4/7 : UG4 (PC) Strength : 10.0
-CH 102_21/26 : UG5 (PC) Strength : 10.0
-ME 201_7/7 : UG5 (PC) Strength : 4.0
-CH 102_1/26 : F300 (PC) Strength : 10.0
-CH 102_12/26 : F300 (PC) Strength : 10.0
-CH 102_13/26 : F300 (PC) Strength : 10.0
-CH 102_15/26 : F300 (PC) Strength : 10.0
-CH 102_16/26 : F300 (PC) Strength : 10.0
-CH 102_17/26 : F300 (PC) Strength : 10.0
-CH 102_18/26 : F300 (PC) Strength : 10.0
-CH 102_26/26 : F300 (PC) Strength : 10.0
-CH 102_4/26 : F300 (PC) Strength : 10.0
-CH 102_5/26 : F300 (PC) Strength : 10.0
-CH 102_6/26 : F300 (PC) Strength : 10.0
-CH 102_7/26 : F300 (PC) Strength : 10.0
-EE 205_2/5 : F300 (PC) Strength : 10.0
-EE 205_5/5 : F300 (PC) Strength : 9.0
-ME 201_2/7 : F300 (PC) Strength : 10.0
-ME 201_5/7 : F300 (PC) Strength : 10.0
-ME 201_6/7 : F300 (PC) Strength : 10.0
-PH 402_12/17 : 21 (WALMI) Strength : 10.0
-PH 402_15/17 : 115 (WALMI) Strength : 10.0
-EE 610_2/3 : 119 (WALMI) Strength : 8.0
-CL 802_1/1 : 22 (WALMI) Strength : 3.0
-EE 610_1/3 : 117 (WALMI) Strength : 8.0
-PH 402_14/17 : 117 (WALMI) Strength : 10.0
-PH 402_8/17 : 117 (WALMI) Strength : 10.0
-PH 402_11/17 : 23 (WALMI) Strength : 10.0
-PH 402_2/17 : 23 (WALMI) Strength : 10.0
-PH 402_3/17 : 23 (WALMI) Strength : 10.0
-PH 402_5/17 : 23 (WALMI) Strength : 10.0
-PH 402_6/17 : 23 (WALMI) Strength : 10.0
-PH 402_7/17 : Central Hall (WALMI) Strength : 10.0
-PH 402_17/17 : 214 (WALMI) Strength : 2.0
-EE 610_3/3 : 215 (WALMI) Strength : 8.0
-PH 402_9/17 : 215 (WALMI) Strength : 10.0
-PH 402_1/17 : 203 (WALMI) Strength : 10.0
-PH 402_16/17 : 203 (WALMI) Strength : 10.0
-PH 402_10/17 : Auditorium (WALMI) Strength : 10.0
-PH 402_13/17 : Auditorium (WALMI) Strength : 10.0
-PH 402_4/17 : Auditorium (WALMI) Strength : 10.0</t>
+          <t>CE 203
+CH 102
+CL 802
+CS 403
+CS 609
+EE 210
+EE 325
+EE 622
+ME 324
+ME 621</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>CL 201_1/2 : UG2 (PC) Strength : 6.0
-ME 207_5/6 : UG2 (PC) Strength : 9.0
-MA 209_1/3 : UG3 (PC) Strength : 10.0
-ME 207_4/6 : UG3 (PC) Strength : 9.0
-ME 207_6/6 : UG3 (PC) Strength : 7.0
-CL 201_2/2 : UG4 (PC) Strength : 6.0
-MA 209_3/3 : UG4 (PC) Strength : 10.0
-ME 207_1/6 : UG5 (PC) Strength : 9.0
-ME 207_3/6 : UG5 (PC) Strength : 9.0
-MA 209_2/3 : F300 (PC) Strength : 10.0
-ME 207_2/6 : F300 (PC) Strength : 9.0
-CE 602_1/1 : 21 (WALMI) Strength : 6.0
-EE 420_1/3 : 115 (WALMI) Strength : 8.0
-CS 609_1/2 : 119 (WALMI) Strength : 6.0
-BB 810_1/1 : 22 (WALMI) Strength : 6.0
-ME 630_1/1 : Central Hall (WALMI) Strength : 4.0
-EE 420_2/3 : 215 (WALMI) Strength : 8.0
-EE 420_3/3 : 215 (WALMI) Strength : 8.0
-ME 607_1/1 : 203 (WALMI) Strength : 10.0
-CS 609_2/2 : Auditorium (WALMI) Strength : 5.0</t>
+          <t>CL 201
+HS 501
+MA 209
+ME 212
+PH 402</t>
         </is>
       </c>
     </row>
@@ -649,102 +513,24 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>EE 229_2/6 : UG3 (PC) Strength : 10.0
-EE 229_4/6 : UG5 (PC) Strength : 10.0
-EE 229_1/6 : F300 (PC) Strength : 10.0
-EE 229_3/6 : F300 (PC) Strength : 10.0
-EE 229_5/6 : F300 (PC) Strength : 10.0
-EE 229_6/6 : F300 (PC) Strength : 10.0
-CS 303_2/8 : 115 (WALMI) Strength : 10.0
-EE 690_1/4 : 119 (WALMI) Strength : 8.0
-CS 303_7/8 : 117 (WALMI) Strength : 10.0
-CS 303_8/8 : 117 (WALMI) Strength : 10.0
-CS 303_4/8 : 23 (WALMI) Strength : 10.0
-EE 690_3/4 : 23 (WALMI) Strength : 8.0
-EE 690_4/4 : 23 (WALMI) Strength : 8.0
-CS 303_3/8 : Central Hall (WALMI) Strength : 10.0
-EE 690_2/4 : 214 (WALMI) Strength : 8.0
-CS 303_1/8 : 215 (WALMI) Strength : 10.0
-CS 303_5/8 : Auditorium (WALMI) Strength : 10.0
-CS 303_6/8 : Auditorium (WALMI) Strength : 10.0</t>
+          <t>BB 301
+BB 810
+CS 213
+CS 621
+EE 631
+EE 688
+ME 421
+ME 643
+PH 302</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>BB 103_21/25 : UG1 (PC) Strength : 10.0
-BB 103_4/25 : UG1 (PC) Strength : 10.0
-EE 221_4/21 : UG1 (PC) Strength : 10.0
-BB 103_13/25 : UG2 (PC) Strength : 10.0
-BB 103_18/25 : UG2 (PC) Strength : 10.0
-BB 103_3/25 : UG2 (PC) Strength : 10.0
-EE 221_13/21 : UG2 (PC) Strength : 10.0
-EE 221_18/21 : UG2 (PC) Strength : 10.0
-EE 221_20/21 : UG2 (PC) Strength : 10.0
-BB 103_14/25 : UG3 (PC) Strength : 10.0
-BB 103_2/25 : UG3 (PC) Strength : 10.0
-BB 103_8/25 : UG3 (PC) Strength : 10.0
-EE 221_16/21 : UG3 (PC) Strength : 10.0
-EE 221_9/21 : UG3 (PC) Strength : 10.0
-BB 103_1/25 : UG4 (PC) Strength : 10.0
-BB 103_11/25 : UG4 (PC) Strength : 10.0
-BB 103_16/25 : UG4 (PC) Strength : 10.0
-BB 103_25/25 : UG4 (PC) Strength : 9.0
-BB 103_5/25 : UG4 (PC) Strength : 10.0
-EE 221_1/21 : UG4 (PC) Strength : 10.0
-EE 221_11/21 : UG4 (PC) Strength : 10.0
-EE 221_2/21 : UG4 (PC) Strength : 10.0
-EE 221_8/21 : UG4 (PC) Strength : 10.0
-EE 221_15/21 : UG5 (PC) Strength : 10.0
-BB 103_19/25 : UG6 (PC) Strength : 10.0
-BB 103_10/25 : F300 (PC) Strength : 10.0
-BB 103_12/25 : F300 (PC) Strength : 10.0
-BB 103_15/25 : F300 (PC) Strength : 10.0
-BB 103_17/25 : F300 (PC) Strength : 10.0
-BB 103_20/25 : F300 (PC) Strength : 10.0
-BB 103_22/25 : F300 (PC) Strength : 10.0
-BB 103_23/25 : F300 (PC) Strength : 10.0
-BB 103_24/25 : F300 (PC) Strength : 10.0
-BB 103_6/25 : F300 (PC) Strength : 10.0
-BB 103_7/25 : F300 (PC) Strength : 10.0
-BB 103_9/25 : F300 (PC) Strength : 10.0
-CE 202_1/2 : F300 (PC) Strength : 6.0
-CE 202_2/2 : F300 (PC) Strength : 6.0
-EE 221_10/21 : F300 (PC) Strength : 10.0
-EE 221_12/21 : F300 (PC) Strength : 10.0
-EE 221_14/21 : F300 (PC) Strength : 10.0
-EE 221_17/21 : F300 (PC) Strength : 10.0
-EE 221_19/21 : F300 (PC) Strength : 10.0
-EE 221_21/21 : F300 (PC) Strength : 7.0
-EE 221_3/21 : F300 (PC) Strength : 10.0
-EE 221_5/21 : F300 (PC) Strength : 10.0
-EE 221_6/21 : F300 (PC) Strength : 10.0
-EE 221_7/21 : F300 (PC) Strength : 10.0
-EE 325_5/5 : 21 (WALMI) Strength : 9.0
-EE 616_2/4 : 21 (WALMI) Strength : 10.0
-EE 325_3/5 : 115 (WALMI) Strength : 9.0
-ME 220_2/4 : 115 (WALMI) Strength : 10.0
-ME 903_2/3 : 115 (WALMI) Strength : 10.0
-CS 301_1/8 : 22 (WALMI) Strength : 10.0
-CS 301_7/8 : 22 (WALMI) Strength : 10.0
-EE 325_2/5 : 22 (WALMI) Strength : 9.0
-ME 220_4/4 : 22 (WALMI) Strength : 10.0
-CS 301_6/8 : 117 (WALMI) Strength : 10.0
-ME 903_1/3 : 117 (WALMI) Strength : 10.0
-CS 301_3/8 : 23 (WALMI) Strength : 10.0
-EE 325_1/5 : 23 (WALMI) Strength : 9.0
-EE 616_3/4 : 23 (WALMI) Strength : 10.0
-CS 301_4/8 : Central Hall (WALMI) Strength : 10.0
-CS 607_2/2 : Central Hall (WALMI) Strength : 5.0
-ME 903_3/3 : Central Hall (WALMI) Strength : 9.0
-EE 616_1/4 : 214 (WALMI) Strength : 10.0
-ME 220_3/4 : 214 (WALMI) Strength : 10.0
-CS 301_2/8 : 215 (WALMI) Strength : 10.0
-CS 607_1/2 : 215 (WALMI) Strength : 6.0
-EE 325_4/5 : 215 (WALMI) Strength : 9.0
-ME 220_1/4 : 215 (WALMI) Strength : 10.0
-CS 301_5/8 : 203 (WALMI) Strength : 10.0
-CS 301_8/8 : 203 (WALMI) Strength : 6.0
-EE 616_4/4 : Auditorium (WALMI) Strength : 8.0</t>
+          <t>CE 202
+CS 101
+EE 205
+EE 629
+ME 207</t>
         </is>
       </c>
     </row>
@@ -756,85 +542,27 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>CS 101_17/26 : UG1 (PC) Strength : 10.0
-CS 101_23/26 : UG1 (PC) Strength : 10.0
-CS 101_1/26 : UG2 (PC) Strength : 10.0
-CS 101_11/26 : UG2 (PC) Strength : 10.0
-CS 101_25/26 : UG2 (PC) Strength : 10.0
-CS 101_12/26 : UG3 (PC) Strength : 10.0
-CS 101_15/26 : UG3 (PC) Strength : 10.0
-CS 101_19/26 : UG4 (PC) Strength : 10.0
-CS 101_20/26 : UG4 (PC) Strength : 10.0
-CS 101_6/26 : UG4 (PC) Strength : 10.0
-CS 101_7/26 : UG4 (PC) Strength : 10.0
-CS 101_8/26 : UG4 (PC) Strength : 10.0
-CS 101_3/26 : UG5 (PC) Strength : 10.0
-CS 101_26/26 : UG6 (PC) Strength : 6.0
-CS 101_5/26 : UG6 (PC) Strength : 10.0
-CS 101_10/26 : F300 (PC) Strength : 10.0
-CS 101_13/26 : F300 (PC) Strength : 10.0
-CS 101_14/26 : F300 (PC) Strength : 10.0
-CS 101_16/26 : F300 (PC) Strength : 10.0
-CS 101_18/26 : F300 (PC) Strength : 10.0
-CS 101_2/26 : F300 (PC) Strength : 10.0
-CS 101_21/26 : F300 (PC) Strength : 10.0
-CS 101_22/26 : F300 (PC) Strength : 10.0
-CS 101_24/26 : F300 (PC) Strength : 10.0
-CS 101_4/26 : F300 (PC) Strength : 10.0
-CS 101_9/26 : F300 (PC) Strength : 10.0
-CS 403_2/3 : 115 (WALMI) Strength : 8.0
-EE 688_2/3 : 22 (WALMI) Strength : 9.0
-PH 302_1/1 : 117 (WALMI) Strength : 7.0
-EE 688_1/3 : 214 (WALMI) Strength : 9.0
-CS 403_1/3 : 215 (WALMI) Strength : 8.0
-EE 688_3/3 : 203 (WALMI) Strength : 7.0
-CS 403_3/3 : Auditorium (WALMI) Strength : 7.0</t>
+          <t>CE 602
+CS 203
+CS 601
+EE 621
+EE 691
+MA 201
+MA 321
+ME 201
+ME 305
+ME 446
+ME 608
+PH 101
+PH 304</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>EE 210_2/6 : UG1 (PC) Strength : 10.0
-EE 210_1/6 : UG2 (PC) Strength : 10.0
-EE 210_3/6 : UG2 (PC) Strength : 10.0
-EE 210_5/6 : UG3 (PC) Strength : 10.0
-EE 210_4/6 : UG4 (PC) Strength : 10.0
-EE 210_6/6 : UG5 (PC) Strength : 10.0
-HS 433_8/9 : 21 (WALMI) Strength : 9.0
-HS 409_15/16 : 115 (WALMI) Strength : 10.0
-HS 409_4/16 : 115 (WALMI) Strength : 10.0
-HS 409_7/16 : 115 (WALMI) Strength : 10.0
-HS 425_1/3 : 115 (WALMI) Strength : 8.0
-HS 409_16/16 : 119 (WALMI) Strength : 7.0
-ME 309_3/4 : 119 (WALMI) Strength : 10.0
-HS 409_14/16 : 22 (WALMI) Strength : 10.0
-HS 433_1/9 : 22 (WALMI) Strength : 9.0
-ME 309_2/4 : 22 (WALMI) Strength : 10.0
-HS 409_11/16 : 117 (WALMI) Strength : 10.0
-HS 433_6/9 : 117 (WALMI) Strength : 9.0
-ME 309_1/4 : 117 (WALMI) Strength : 10.0
-HS 409_1/16 : 23 (WALMI) Strength : 10.0
-HS 409_6/16 : 23 (WALMI) Strength : 10.0
-HS 409_8/16 : 23 (WALMI) Strength : 10.0
-HS 433_5/9 : 23 (WALMI) Strength : 9.0
-HS 433_7/9 : 23 (WALMI) Strength : 9.0
-HS 425_3/3 : Central Hall (WALMI) Strength : 6.0
-HS 433_2/9 : Central Hall (WALMI) Strength : 9.0
-HS 409_3/16 : 214 (WALMI) Strength : 10.0
-HS 433_4/9 : 214 (WALMI) Strength : 9.0
-EE 634_4/4 : 215 (WALMI) Strength : 9.0
-HS 409_10/16 : 215 (WALMI) Strength : 10.0
-HS 433_3/9 : 215 (WALMI) Strength : 9.0
-EE 634_2/4 : 203 (WALMI) Strength : 10.0
-HS 409_2/16 : 203 (WALMI) Strength : 10.0
-HS 409_5/16 : 203 (WALMI) Strength : 10.0
-HS 433_9/9 : 203 (WALMI) Strength : 9.0
-EE 634_1/4 : Auditorium (WALMI) Strength : 10.0
-EE 634_3/4 : Auditorium (WALMI) Strength : 10.0
-HS 409_12/16 : Auditorium (WALMI) Strength : 10.0
-HS 409_13/16 : Auditorium (WALMI) Strength : 10.0
-HS 409_9/16 : Auditorium (WALMI) Strength : 10.0
-HS 425_2/3 : Auditorium (WALMI) Strength : 8.0
-ME 309_4/4 : Auditorium (WALMI) Strength : 10.0</t>
+          <t>EE 601
+MA 203
+ME 222
+ME 609</t>
         </is>
       </c>
     </row>
@@ -846,81 +574,24 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>HS 201_13/23 : UG1 (PC) Strength : 10.0
-HS 201_5/23 : UG1 (PC) Strength : 10.0
-HS 201_4/23 : UG2 (PC) Strength : 10.0
-HS 201_7/23 : UG2 (PC) Strength : 10.0
-HS 201_8/23 : UG2 (PC) Strength : 10.0
-HS 201_15/23 : UG3 (PC) Strength : 10.0
-HS 201_2/23 : UG3 (PC) Strength : 10.0
-HS 201_17/23 : UG4 (PC) Strength : 10.0
-HS 201_3/23 : UG4 (PC) Strength : 10.0
-HS 201_6/23 : UG4 (PC) Strength : 10.0
-HS 201_9/23 : UG4 (PC) Strength : 10.0
-HS 201_16/23 : UG5 (PC) Strength : 10.0
-HS 201_23/23 : UG5 (PC) Strength : 1.0
-HS 201_1/23 : F300 (PC) Strength : 10.0
-HS 201_10/23 : F300 (PC) Strength : 10.0
-HS 201_11/23 : F300 (PC) Strength : 10.0
-HS 201_12/23 : F300 (PC) Strength : 10.0
-HS 201_14/23 : F300 (PC) Strength : 10.0
-HS 201_18/23 : F300 (PC) Strength : 10.0
-HS 201_19/23 : F300 (PC) Strength : 10.0
-HS 201_20/23 : F300 (PC) Strength : 10.0
-HS 201_21/23 : F300 (PC) Strength : 10.0
-HS 201_22/23 : F300 (PC) Strength : 10.0
-EE 321_1/6 : 21 (WALMI) Strength : 9.0
-EE 321_2/6 : 115 (WALMI) Strength : 9.0
-EE 321_6/6 : 115 (WALMI) Strength : 8.0
-EE 321_4/6 : 119 (WALMI) Strength : 9.0
-EE 622_3/3 : 22 (WALMI) Strength : 9.0
-ME 446_1/1 : 117 (WALMI) Strength : 10.0
-PH 425_3/5 : 23 (WALMI) Strength : 9.0
-PH 425_5/5 : 23 (WALMI) Strength : 7.0
-EE 321_3/6 : Central Hall (WALMI) Strength : 9.0
-PH 425_2/5 : Central Hall (WALMI) Strength : 9.0
-PH 425_4/5 : 215 (WALMI) Strength : 9.0
-EE 321_5/6 : 203 (WALMI) Strength : 9.0
-EE 622_1/3 : 203 (WALMI) Strength : 9.0
-EE 622_2/3 : Auditorium (WALMI) Strength : 9.0
-PH 425_1/5 : Auditorium (WALMI) Strength : 9.0</t>
+          <t>BB 103
+CS 303
+CS 607
+EE 221
+EE 227
+EE 321
+EE 690
+ME 309
+ME 903</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>CS 213_2/17 : UG1 (PC) Strength : 10.0
-CS 213_3/17 : UG1 (PC) Strength : 10.0
-CS 213_16/17 : UG2 (PC) Strength : 10.0
-CS 213_9/17 : UG2 (PC) Strength : 10.0
-MA 201_2/5 : UG2 (PC) Strength : 10.0
-CS 213_1/17 : UG3 (PC) Strength : 10.0
-CS 213_10/17 : UG3 (PC) Strength : 10.0
-CS 213_8/17 : UG3 (PC) Strength : 10.0
-MA 201_3/5 : UG3 (PC) Strength : 10.0
-CS 213_11/17 : UG4 (PC) Strength : 10.0
-CS 213_13/17 : UG4 (PC) Strength : 10.0
-CS 213_14/17 : UG4 (PC) Strength : 10.0
-CS 213_6/17 : UG4 (PC) Strength : 10.0
-CS 213_7/17 : UG4 (PC) Strength : 10.0
-MA 201_1/5 : UG4 (PC) Strength : 10.0
-MA 201_4/5 : UG4 (PC) Strength : 10.0
-MA 201_5/5 : UG4 (PC) Strength : 10.0
-ME 222_2/2 : UG4 (PC) Strength : 6.0
-CS 213_17/17 : UG5 (PC) Strength : 6.0
-CS 213_4/17 : UG5 (PC) Strength : 10.0
-CS 213_12/17 : UG6 (PC) Strength : 10.0
-ME 222_1/2 : UG6 (PC) Strength : 6.0
-CS 213_15/17 : F300 (PC) Strength : 10.0
-CS 213_5/17 : F300 (PC) Strength : 10.0
-EE 621_1/3 : 21 (WALMI) Strength : 9.0
-EE 621_2/3 : 115 (WALMI) Strength : 9.0
-CS 621_1/2 : 119 (WALMI) Strength : 10.0
-CS 621_2/2 : 22 (WALMI) Strength : 9.0
-EE 691_1/2 : 214 (WALMI) Strength : 8.0
-EE 691_2/2 : 215 (WALMI) Strength : 7.0
-EE 621_3/3 : 203 (WALMI) Strength : 9.0
-ME 605_2/2 : 203 (WALMI) Strength : 7.0
-ME 605_1/2 : Auditorium (WALMI) Strength : 7.0</t>
+          <t>CE 201
+CS 810
+HS 106
+ME 204
+PH 103</t>
         </is>
       </c>
     </row>
@@ -932,72 +603,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>MA 101_18/26 : UG1 (PC) Strength : 10.0
-MA 101_5/26 : UG1 (PC) Strength : 10.0
-MA 101_13/26 : UG2 (PC) Strength : 10.0
-MA 101_25/26 : UG2 (PC) Strength : 10.0
-MA 101_4/26 : UG2 (PC) Strength : 10.0
-CE 203_1/2 : UG3 (PC) Strength : 6.0
-MA 101_2/26 : UG3 (PC) Strength : 10.0
-MA 101_8/26 : UG3 (PC) Strength : 10.0
-MA 101_9/26 : UG3 (PC) Strength : 10.0
-MA 101_1/26 : UG4 (PC) Strength : 10.0
-MA 101_14/26 : UG4 (PC) Strength : 10.0
-MA 101_17/26 : UG4 (PC) Strength : 10.0
-MA 101_20/26 : UG4 (PC) Strength : 10.0
-MA 101_26/26 : UG4 (PC) Strength : 4.0
-MA 101_24/26 : UG5 (PC) Strength : 10.0
-CE 203_2/2 : F300 (PC) Strength : 6.0
-MA 101_10/26 : F300 (PC) Strength : 10.0
-MA 101_11/26 : F300 (PC) Strength : 10.0
-MA 101_12/26 : F300 (PC) Strength : 10.0
-MA 101_15/26 : F300 (PC) Strength : 10.0
-MA 101_16/26 : F300 (PC) Strength : 10.0
-MA 101_19/26 : F300 (PC) Strength : 10.0
-MA 101_21/26 : F300 (PC) Strength : 10.0
-MA 101_22/26 : F300 (PC) Strength : 10.0
-MA 101_23/26 : F300 (PC) Strength : 10.0
-MA 101_3/26 : F300 (PC) Strength : 10.0
-MA 101_6/26 : F300 (PC) Strength : 10.0
-MA 101_7/26 : F300 (PC) Strength : 10.0
-EE 629_11/11 : 21 (WALMI) Strength : 1.0
-EE 629_5/11 : 21 (WALMI) Strength : 10.0
-EE 629_10/11 : 115 (WALMI) Strength : 10.0
-EE 629_6/11 : 115 (WALMI) Strength : 10.0
-EE 629_1/11 : 117 (WALMI) Strength : 10.0
-ME 609_1/2 : 117 (WALMI) Strength : 9.0
-EE 629_8/11 : 23 (WALMI) Strength : 10.0
-ME 609_2/2 : 23 (WALMI) Strength : 8.0
-EE 629_3/11 : Central Hall (WALMI) Strength : 10.0
-EE 629_4/11 : 215 (WALMI) Strength : 10.0
-EE 629_7/11 : 203 (WALMI) Strength : 10.0
-EE 629_9/11 : 203 (WALMI) Strength : 10.0
-EE 629_2/11 : Auditorium (WALMI) Strength : 10.0</t>
+          <t>CL 204
+CS 301
+EE 420
+EE 607
+EE 689
+HS 201
+ME 311
+ME 605
+PH 201</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>BB 301_3/5 : UG1 (PC) Strength : 9.0
-BB 301_5/5 : UG2 (PC) Strength : 6.0
-BB 301_2/5 : UG6 (PC) Strength : 9.0
-BB 301_4/5 : UG6 (PC) Strength : 9.0
-BB 301_1/5 : F300 (PC) Strength : 9.0
-CS 601_1/6 : 21 (WALMI) Strength : 10.0
-EE 601_4/5 : 115 (WALMI) Strength : 9.0
-ME 324_4/4 : 119 (WALMI) Strength : 10.0
-CS 601_2/6 : 22 (WALMI) Strength : 10.0
-ME 324_2/4 : 22 (WALMI) Strength : 10.0
-CS 601_4/6 : 117 (WALMI) Strength : 10.0
-ME 324_3/4 : 117 (WALMI) Strength : 10.0
-CS 601_5/6 : 23 (WALMI) Strength : 10.0
-EE 601_3/5 : 23 (WALMI) Strength : 9.0
-ME 324_1/4 : Central Hall (WALMI) Strength : 10.0
-EE 601_5/5 : 215 (WALMI) Strength : 5.0
-EE 601_1/5 : 203 (WALMI) Strength : 9.0
-CS 601_3/6 : Auditorium (WALMI) Strength : 10.0
-CS 601_6/6 : Auditorium (WALMI) Strength : 10.0
-EE 601_2/5 : Auditorium (WALMI) Strength : 9.0
-EE 607_1/1 : Auditorium (WALMI) Strength : 9.0</t>
+          <t>EE 610
+HS 103
+PH 425</t>
         </is>
       </c>
     </row>
